--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$209</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3328,22 +3328,22 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -4274,22 +4274,22 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4311,22 +4311,22 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -8822,7 +8822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8917,12 +8917,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -8983,12 +8983,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
@@ -9005,12 +9005,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 5</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
         </is>
       </c>
     </row>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 5</t>
         </is>
       </c>
     </row>
@@ -9049,34 +9049,34 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 12</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 12</t>
         </is>
       </c>
     </row>
@@ -9088,17 +9088,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9132,61 +9132,61 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>cedeu 3 de 26 aulas (11.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu 3 de 26 aulas (11.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9203,12 +9203,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Redação / ACo (Alexandre Braga Badaue Coelho)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9220,17 +9220,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
+          <t>tem 3 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9242,17 +9242,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Redação / ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9313,12 +9313,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
@@ -9330,61 +9330,61 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Mat / JJ (João Jorge Fernandes Chaves)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9396,17 +9396,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9418,68 +9418,68 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Mat / JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Redação / AMu (André Barros Mucci)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -9489,41 +9489,41 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 5 (meta: no máximo 2)</t>
+          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Redação / AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu 5 de 38 aulas (13.2%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -9533,34 +9533,34 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artes / </t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>tem 3 aulas semanais e cedeu 5 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu 5 de 38 aulas (13.2%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9572,17 +9572,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t xml:space="preserve">Artes / </t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9616,61 +9616,61 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artes / </t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9682,17 +9682,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t xml:space="preserve">Artes / </t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9709,17 +9709,61 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
           <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>cedeu aula na semana 16 tendo prova própria na semana 16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D41"/>
+  <autoFilter ref="A2:D43"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$209</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3328,22 +3328,22 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -4274,22 +4274,22 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4311,22 +4311,22 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -7043,22 +7043,18 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr"/>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -7080,18 +7076,22 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
@@ -8092,18 +8092,18 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
+          <t>10º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr"/>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
@@ -8822,7 +8822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8917,12 +8917,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -8983,12 +8983,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
@@ -9005,12 +9005,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 5</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
         </is>
       </c>
     </row>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 5</t>
         </is>
       </c>
     </row>
@@ -9049,34 +9049,34 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 12</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 12</t>
         </is>
       </c>
     </row>
@@ -9088,17 +9088,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9132,61 +9132,61 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>cedeu 3 de 26 aulas (11.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu 3 de 26 aulas (11.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9203,12 +9203,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Redação / ACo (Alexandre Braga Badaue Coelho)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9220,17 +9220,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
+          <t>tem 3 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9242,17 +9242,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Redação / ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9313,12 +9313,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
@@ -9330,61 +9330,61 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Mat / JJ (João Jorge Fernandes Chaves)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9396,17 +9396,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9418,68 +9418,68 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Mat / JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Redação / AMu (André Barros Mucci)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -9489,41 +9489,41 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 5 (meta: no máximo 2)</t>
+          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Redação / AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu 5 de 38 aulas (13.2%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -9533,34 +9533,34 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artes / </t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>tem 3 aulas semanais e cedeu 5 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu 5 de 38 aulas (13.2%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9572,17 +9572,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t xml:space="preserve">Artes / </t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9616,61 +9616,61 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artes / </t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9682,17 +9682,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t xml:space="preserve">Artes / </t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9709,17 +9709,61 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
           <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>cedeu aula na semana 16 tendo prova própria na semana 16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D41"/>
+  <autoFilter ref="A2:D43"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$209</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7293,32 +7293,32 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7335,22 +7335,22 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7367,27 +7367,23 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>Fab (Fabio Merçon)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr"/>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
@@ -7409,18 +7405,22 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>5º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7479,22 +7479,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 12)</t>
+          <t>6º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 6º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7511,27 +7511,27 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qui, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 6º de Mat para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7585,32 +7585,28 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr"/>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7622,27 +7618,27 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -7659,23 +7655,27 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
@@ -7692,32 +7692,32 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>10º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -8305,32 +8305,32 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8347,22 +8347,22 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -8379,27 +8379,23 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D198" s="6" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr"/>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
@@ -8416,28 +8412,32 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 5º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8449,27 +8449,27 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 12)</t>
+          <t>5º, 6º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 5º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º, 6º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8523,32 +8523,28 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>5º, 6º tempo(s) (Seg, semana 13)</t>
-        </is>
-      </c>
-      <c r="D202" s="6" t="inlineStr">
-        <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr"/>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º, 6º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8556,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -8597,28 +8593,32 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D204" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9511,34 +9511,34 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Redação / AMu (André Barros Mucci)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Redação / AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 5 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -9560,51 +9560,51 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>cedeu 5 de 38 aulas (13.2%) — acima do teto de 11%</t>
+          <t>tem 3 aulas semanais e cedeu 5 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artes / </t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu 5 de 38 aulas (13.2%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9616,17 +9616,17 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t xml:space="preserve">Artes / </t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9660,61 +9660,61 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artes / </t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9726,17 +9726,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t xml:space="preserve">Artes / </t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9753,17 +9753,61 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
           <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>cedeu aula na semana 16 tendo prova própria na semana 16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D43"/>
+  <autoFilter ref="A2:D45"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$209</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2197,18 +2197,22 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2999,18 +3003,22 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
+          <t>9º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -3022,37 +3030,37 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>6º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Raf (Rafael Alverne Freitas de Albuquerque) a cessão do(s) tempo(s) 5º de Redação para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3064,27 +3072,27 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Ter, semana 4)</t>
+          <t>1º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -3106,22 +3114,22 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -3138,12 +3146,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>3º tempo(s) (Sex, semana 5)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3158,12 +3166,12 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Qui</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3180,22 +3188,22 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 5)</t>
+          <t>4º tempo(s) (Sex, semana 5)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 4º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3212,32 +3220,32 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 5)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 4º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3249,32 +3257,32 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3286,27 +3294,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3323,12 +3331,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -3343,7 +3351,7 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -3360,27 +3368,23 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3402,18 +3406,22 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3430,32 +3438,32 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3475,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -3487,12 +3495,12 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3504,27 +3512,27 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>1º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -3546,22 +3554,22 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 12)</t>
+          <t>2º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3578,27 +3586,27 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3615,27 +3623,23 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -3657,18 +3661,22 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+        </is>
+      </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3685,27 +3693,27 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 12)</t>
+          <t>4º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3727,22 +3735,22 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 13)</t>
+          <t>5º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3759,27 +3767,27 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -3796,27 +3804,27 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -3833,27 +3841,27 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
+          <t>10º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -3875,22 +3883,22 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 14)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -3907,32 +3915,32 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3944,69 +3952,69 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4018,27 +4026,27 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -4060,22 +4068,22 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>3º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -4092,34 +4100,26 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>FBri (Fábio Luís de Brito)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -4129,26 +4129,34 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 5)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Qui</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -4158,32 +4166,32 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 5)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4195,32 +4203,32 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4232,27 +4240,27 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -4274,22 +4282,22 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4306,27 +4314,27 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>1º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 1º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4348,22 +4356,22 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 1º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4380,27 +4388,23 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr"/>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4417,28 +4421,32 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 10)</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4450,32 +4458,32 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4492,22 +4500,22 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4524,12 +4532,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4544,7 +4552,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -4566,22 +4574,22 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 12)</t>
+          <t>3º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -4598,27 +4606,23 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 12)</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>FBri (Fábio Luís de Brito)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -4635,23 +4639,27 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -4668,27 +4676,27 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4705,27 +4713,27 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -4742,27 +4750,27 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -4779,27 +4787,27 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -4816,32 +4824,32 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4853,32 +4861,32 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4895,22 +4903,22 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>11º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -4922,39 +4930,35 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -4964,30 +4968,34 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 4)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -4997,27 +5005,27 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>9º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -5039,22 +5047,18 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5071,23 +5075,27 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Hist</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -5109,22 +5117,22 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
+          <t>11º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 11º de Fis para a prova de Hist</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5141,32 +5149,28 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr"/>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 11º de Fis para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5178,28 +5182,32 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr"/>
+          <t>1º, 2º tempo(s) (Qui, semana 6)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º, 2º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5211,27 +5219,27 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>1º, 2º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º, 2º de Fis para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -5253,22 +5261,22 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -5285,27 +5293,27 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>2º, 3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -5322,27 +5330,27 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -5364,22 +5372,22 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -5396,32 +5404,32 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>4º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 4º de Redação para a prova de GL</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5433,32 +5441,32 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 8)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 4º de Redação para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5470,34 +5478,30 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -5507,30 +5511,30 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 12)</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 11C2</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -5540,28 +5544,32 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5573,27 +5581,27 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -5615,22 +5623,18 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -5647,23 +5651,27 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -5680,32 +5688,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr"/>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5717,28 +5721,32 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr"/>
+          <t>6º tempo(s) (Seg, semana 16)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5755,22 +5763,22 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>7º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -5787,27 +5795,23 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -5824,23 +5828,27 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -5862,22 +5870,22 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5894,27 +5902,27 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>1º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -5936,22 +5944,22 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -5963,37 +5971,37 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Geo</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6010,22 +6018,22 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>3º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -6042,27 +6050,23 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6079,23 +6083,27 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -6112,32 +6120,28 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr"/>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6149,28 +6153,32 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qui, semana 6)</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 2º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6182,27 +6190,27 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 2º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -6219,17 +6227,17 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -6239,7 +6247,7 @@
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -6256,27 +6264,27 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -6293,32 +6301,32 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>4º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de GL</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6330,32 +6338,32 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 8)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6367,34 +6375,30 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -6404,30 +6408,30 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 11C1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -6437,28 +6441,32 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6475,22 +6483,22 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
+          <t>3º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 3º de Qui para a prova de Hist</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -6507,27 +6515,23 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 14)</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 3º de Qui para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6544,23 +6548,27 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr"/>
+          <t>9º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -6582,22 +6590,22 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
@@ -6614,32 +6622,28 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6651,28 +6655,32 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr"/>
+          <t>6º tempo(s) (Seg, semana 16)</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6684,27 +6692,27 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>2º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -6726,22 +6734,18 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
@@ -6758,23 +6762,27 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -6791,27 +6799,27 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
@@ -6823,37 +6831,33 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr"/>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6865,23 +6869,23 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -6903,18 +6907,22 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -6931,27 +6939,27 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
@@ -6968,32 +6976,28 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr"/>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7005,12 +7009,12 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
+          <t>10º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr"/>
@@ -7021,12 +7025,12 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7043,18 +7047,22 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -7071,27 +7079,27 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
@@ -7108,12 +7116,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -7128,12 +7136,12 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7145,32 +7153,32 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7182,27 +7190,27 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -7224,22 +7232,22 @@
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
@@ -7256,27 +7264,27 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7298,22 +7306,22 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -7330,27 +7338,23 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>Fab (Fabio Merçon)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr"/>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7372,18 +7376,22 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
@@ -7400,12 +7408,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>5º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -7420,12 +7428,12 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7442,22 +7450,22 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 12)</t>
+          <t>6º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 6º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -7474,27 +7482,27 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qui, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 6º de Mat para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7511,7 +7519,7 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
@@ -7536,7 +7544,7 @@
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7548,27 +7556,23 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr"/>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -7590,18 +7594,22 @@
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
@@ -7618,27 +7626,27 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -7655,32 +7663,32 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7692,27 +7700,27 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -7729,32 +7737,32 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 6º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7766,27 +7774,27 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 15)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 6º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -7798,37 +7806,37 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
@@ -7840,32 +7848,28 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7882,18 +7886,22 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -7910,27 +7918,23 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr"/>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7947,23 +7951,27 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
@@ -7985,22 +7993,22 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -8017,32 +8025,28 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
-        <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr"/>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8058,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
+          <t>10º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr"/>
@@ -8070,12 +8074,12 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8087,23 +8091,27 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
@@ -8125,22 +8133,22 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8157,32 +8165,32 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8194,32 +8202,32 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8231,27 +8239,27 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
@@ -8268,27 +8276,27 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -8310,22 +8318,22 @@
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
@@ -8342,27 +8350,23 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr"/>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -8379,28 +8383,32 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D198" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 5º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8412,27 +8420,27 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 12)</t>
+          <t>5º, 6º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 5º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º, 6º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8449,32 +8457,32 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>5º, 6º tempo(s) (Seg, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º, 6º de Ing para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8486,27 +8494,23 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr"/>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -8523,23 +8527,27 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D202" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
@@ -8556,32 +8564,32 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8593,27 +8601,27 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
@@ -8630,32 +8638,32 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 6º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8672,22 +8680,22 @@
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 15)</t>
+          <t>7º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 6º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 7º de Bio para a prova de Qui</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
@@ -8704,27 +8712,27 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 15)</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 7º de Bio para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -8746,22 +8754,22 @@
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
@@ -8770,45 +8778,8 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F209" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G209" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G209"/>
+  <autoFilter ref="A2:G208"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -8822,7 +8793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9621,12 +9592,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artes / </t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9638,17 +9609,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
@@ -9665,12 +9636,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9653,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -9692,29 +9663,29 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
@@ -9726,17 +9697,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artes / </t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
@@ -9753,61 +9724,17 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>cedeu aula na semana 16 tendo prova própria na semana 16</t>
+          <t>cedeu aula na semana 16 tendo prova própria na semana 17</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D45"/>
+  <autoFilter ref="A2:D43"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$208</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3698,22 +3698,22 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 13)</t>
+          <t>7º tempo(s) (Ter, semana 13)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 7º de Bio para a prova de Qui</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3730,27 +3730,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -3804,27 +3804,27 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
+          <t>10º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 14)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -3878,32 +3878,32 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3915,69 +3915,69 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3989,27 +3989,27 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -4031,22 +4031,22 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>3º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -4063,34 +4063,26 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>FBri (Fábio Luís de Brito)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr"/>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -4100,26 +4092,34 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 5)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Qui</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -4129,32 +4129,32 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 5)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4166,32 +4166,32 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4203,27 +4203,27 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -4277,27 +4277,27 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>1º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 1º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 1º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4351,27 +4351,23 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr"/>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4388,28 +4384,32 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 10)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4421,32 +4421,32 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>2º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4458,27 +4458,27 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4495,27 +4495,27 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4532,27 +4532,23 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 12)</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -4569,27 +4565,27 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -4606,23 +4602,27 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Seg, semana 13)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+        </is>
+      </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -4676,27 +4676,27 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 13)</t>
+          <t>2º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4713,27 +4713,27 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -4750,32 +4750,32 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4787,27 +4787,27 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -4824,106 +4824,102 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>11º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4935,30 +4931,34 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 4)</t>
+          <t>9º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -4968,27 +4968,23 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr"/>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -5005,27 +5001,27 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
+          <t>10º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Hist</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -5042,23 +5038,27 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 11º de Fis para a prova de Hist</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5075,32 +5075,28 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr"/>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5112,12 +5108,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>1º, 2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -5132,7 +5128,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 11º de Fis para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º, 2º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5149,28 +5145,32 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5182,27 +5182,27 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>1º, 2º tempo(s) (Qui, semana 6)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º, 2º de Fis para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -5219,27 +5219,27 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
+          <t>2º, 3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -5256,27 +5256,27 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -5293,27 +5293,27 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 7)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -5330,32 +5330,32 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
+          <t>4º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 4º de Redação para a prova de GL</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5367,27 +5367,27 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -5404,34 +5404,30 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 8)</t>
+          <t>6º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 4º de Redação para a prova de GL</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -5441,32 +5437,28 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr"/>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5478,30 +5470,34 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -5511,28 +5507,32 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr"/>
+          <t>9º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5544,27 +5544,23 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -5581,27 +5577,27 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -5618,28 +5614,28 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+          <t>5º tempo(s) (Qua, semana 15)</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5651,27 +5647,27 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -5688,28 +5684,32 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr"/>
+          <t>7º tempo(s) (Seg, semana 16)</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5721,27 +5721,23 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr"/>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5758,27 +5754,27 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
+          <t>4º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -5795,23 +5791,27 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -5828,27 +5828,27 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
+          <t>1º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -5865,27 +5865,27 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5897,74 +5897,74 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Geo</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>3º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5976,27 +5976,23 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr"/>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -6013,27 +6009,27 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -6050,28 +6046,28 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+          <t>7º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6083,27 +6079,27 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 2º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -6120,28 +6116,32 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6153,27 +6153,27 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 2º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -6190,27 +6190,27 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -6227,32 +6227,32 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>4º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de GL</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -6301,34 +6301,30 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 8)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de GL</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -6338,32 +6334,28 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr"/>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6375,30 +6367,34 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -6408,28 +6404,32 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+        </is>
+      </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 3º de Qui para a prova de Hist</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6441,27 +6441,23 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr"/>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
@@ -6478,27 +6474,27 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 14)</t>
+          <t>9º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 3º de Qui para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -6515,23 +6511,27 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6548,32 +6548,28 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6585,27 +6581,27 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
@@ -6622,28 +6618,32 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6655,27 +6655,23 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -6692,27 +6688,27 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -6729,23 +6725,27 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
@@ -6757,74 +6757,66 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr"/>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6836,23 +6828,27 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -6869,23 +6865,27 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -6902,32 +6902,28 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr"/>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -6939,27 +6935,23 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
@@ -6976,28 +6968,32 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7009,23 +7005,27 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
@@ -7042,32 +7042,32 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7079,27 +7079,27 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
@@ -7116,32 +7116,32 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7153,27 +7153,27 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
@@ -7190,27 +7190,27 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -7227,27 +7227,27 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
@@ -7264,27 +7264,23 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr"/>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7301,27 +7297,27 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -7338,28 +7334,32 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7371,32 +7371,32 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>6º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 6º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7408,27 +7408,27 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -7445,32 +7445,32 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qui, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 6º de Mat para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,28 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr"/>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7519,27 +7515,27 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7556,23 +7552,27 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -7589,32 +7589,32 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>10º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7663,32 +7663,32 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 14)</t>
+          <t>6º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 6º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7700,106 +7700,102 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 15)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 6º de Geo para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr"/>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7811,32 +7807,32 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7848,23 +7844,23 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -7881,27 +7877,27 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -7918,23 +7914,27 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>Isb (Isabela Gomes Bustamante)</t>
+        </is>
+      </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7951,32 +7951,28 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr"/>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -7988,27 +7984,23 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr">
-        <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr"/>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -8025,28 +8017,32 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8058,23 +8054,27 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -8091,32 +8091,32 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8128,27 +8128,27 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8165,32 +8165,32 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8202,27 +8202,27 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8239,27 +8239,27 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
@@ -8276,27 +8276,23 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr"/>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -8313,32 +8309,32 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>5º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 5º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8350,28 +8346,32 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr"/>
+          <t>5º, 6º tempo(s) (Seg, semana 13)</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Isb (Isabela Gomes Bustamante)</t>
+        </is>
+      </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º, 6º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8383,32 +8383,32 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 5º de Mat para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8420,32 +8420,28 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>5º, 6º tempo(s) (Seg, semana 13)</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º, 6º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8453,7 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
@@ -8494,28 +8490,32 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8564,32 +8564,32 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 14)</t>
+          <t>6º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 6º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8601,32 +8601,32 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 7º de Bio para a prova de Qui</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8638,27 +8638,27 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 15)</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 6º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -8675,27 +8675,27 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 15)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 7º de Bio para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
@@ -8704,82 +8704,8 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B208" s="6" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C208" s="5" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D208" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E208" s="5" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F208" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G208" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G208"/>
+  <autoFilter ref="A2:G206"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -8793,7 +8719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8844,12 +8770,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8819,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -8910,12 +8836,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8858,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8880,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 5</t>
         </is>
       </c>
     </row>
@@ -8976,12 +8902,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
         </is>
       </c>
     </row>
@@ -8998,41 +8924,41 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 5</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -9042,12 +8968,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 12</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9059,17 +8985,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9017,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9103,61 +9029,61 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu 4 de 26 aulas (15.4%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>cedeu 3 de 26 aulas (11.5%) — acima do teto de 11%</t>
+          <t>tem 3 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9174,12 +9100,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Redação / ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9191,17 +9117,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9213,17 +9139,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Redação / ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
@@ -9240,12 +9166,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
@@ -9284,12 +9210,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9301,61 +9227,61 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Mat / JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9367,17 +9293,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9389,61 +9315,61 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Mat / JJ (João Jorge Fernandes Chaves)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
@@ -9455,46 +9381,46 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Redação / AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
+          <t>tem 3 aulas semanais e cedeu 5 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -9504,12 +9430,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Redação / AMu (André Barros Mucci)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9447,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -9531,51 +9457,51 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 5 (meta: no máximo 2)</t>
+          <t>cedeu 5 de 38 aulas (13.2%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>cedeu 5 de 38 aulas (13.2%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
@@ -9587,7 +9513,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -9597,7 +9523,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9609,24 +9535,24 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -9636,34 +9562,34 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
@@ -9680,61 +9606,17 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
           <t>cedeu aula na semana 16 tendo prova própria na semana 17</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D43"/>
+  <autoFilter ref="A2:D41"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
